--- a/docs/COPY.xlsx
+++ b/docs/COPY.xlsx
@@ -17014,7 +17014,7 @@
     <row r="723">
       <c r="A723" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sb99e77d</t>
+          <t xml:space="preserve">s066beed</t>
         </is>
       </c>
       <c r="C723" s="2" t="inlineStr">
@@ -17024,20 +17024,20 @@
       </c>
       <c r="D723" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">לשחק עם בוט</t>
+          <t xml:space="preserve">כמה הבוט מתאמץ</t>
         </is>
       </c>
       <c r="E723" s="3"/>
       <c r="F723" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Play against a bot</t>
+          <t xml:space="preserve">How hard the bot tries</t>
         </is>
       </c>
     </row>
     <row r="724">
       <c r="A724" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s066beed</t>
+          <t xml:space="preserve">sb99e77d</t>
         </is>
       </c>
       <c r="C724" s="2" t="inlineStr">
@@ -17047,13 +17047,13 @@
       </c>
       <c r="D724" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">כמה הבוט מתאמץ</t>
+          <t xml:space="preserve">לשחק עם בוט</t>
         </is>
       </c>
       <c r="E724" s="3"/>
       <c r="F724" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">How hard the bot tries</t>
+          <t xml:space="preserve">You vs. Bot</t>
         </is>
       </c>
     </row>
@@ -17099,7 +17099,7 @@
       <c r="E726" s="3"/>
       <c r="F726" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Play with friends</t>
+          <t xml:space="preserve">You vs. Friends</t>
         </is>
       </c>
     </row>

--- a/docs/COPY.xlsx
+++ b/docs/COPY.xlsx
@@ -6882,7 +6882,7 @@
       <c r="E282" s="3"/>
       <c r="F282" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Empty {0}</t>
+          <t xml:space="preserve">Clear this side</t>
         </is>
       </c>
     </row>
@@ -7710,7 +7710,7 @@
       <c r="E318" s="3"/>
       <c r="F318" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The side facing you</t>
+          <t xml:space="preserve">The other side</t>
         </is>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
       <c r="E376" s="3"/>
       <c r="F376" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">King {0} carried the battle — {1}% of the damage</t>
+          <t xml:space="preserve">{0}, the King, carried it — {1}% of the damage</t>
         </is>
       </c>
     </row>
@@ -9113,7 +9113,7 @@
       <c r="E379" s="3"/>
       <c r="F379" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">King {0} fell as early as second {1}</t>
+          <t xml:space="preserve">{0}, the King, fell as early as second {1}</t>
         </is>
       </c>
     </row>
@@ -9366,7 +9366,7 @@
       <c r="E390" s="3"/>
       <c r="F390" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">King {0} fell</t>
+          <t xml:space="preserve">{0}, the King, is down</t>
         </is>
       </c>
     </row>
@@ -30871,7 +30871,7 @@
       <c r="E1325" s="3"/>
       <c r="F1325" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Opponent's</t>
+          <t xml:space="preserve">Their</t>
         </is>
       </c>
     </row>
@@ -30894,7 +30894,7 @@
       <c r="E1326" s="3"/>
       <c r="F1326" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Yours</t>
+          <t xml:space="preserve">Your</t>
         </is>
       </c>
     </row>
@@ -30917,7 +30917,7 @@
       <c r="E1327" s="3"/>
       <c r="F1327" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">The {0} King fell. That is the battle.</t>
+          <t xml:space="preserve">{0} King is down. That is the battle.</t>
         </is>
       </c>
     </row>

--- a/docs/COPY.xlsx
+++ b/docs/COPY.xlsx
@@ -16036,7 +16036,7 @@
       <c r="E680" s="3"/>
       <c r="F680" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This week</t>
+          <t xml:space="preserve">Week</t>
         </is>
       </c>
     </row>
@@ -16059,7 +16059,7 @@
       <c r="E681" s="3"/>
       <c r="F681" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">This month</t>
+          <t xml:space="preserve">Month</t>
         </is>
       </c>
     </row>

--- a/docs/COPY.xlsx
+++ b/docs/COPY.xlsx
@@ -1469,7 +1469,7 @@
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">d28e30a0</t>
+          <t xml:space="preserve">d55f84c5</t>
         </is>
       </c>
       <c r="C58" s="2" t="inlineStr">
@@ -1479,7 +1479,7 @@
       </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">אבי-הענקים</t>
+          <t xml:space="preserve">מלך הטיטאנים</t>
         </is>
       </c>
       <c r="E58" s="3"/>
@@ -25450,7 +25450,7 @@
     <row r="1090">
       <c r="A1090" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s1ff71ce</t>
+          <t xml:space="preserve">sb5b05c4</t>
         </is>
       </c>
       <c r="C1090" s="2" t="inlineStr">
@@ -25460,7 +25460,7 @@
       </c>
       <c r="D1090" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">הופה, אבי-הענקים. קלף ענק וחזק. מושלם למשבצת המלך.</t>
+          <t xml:space="preserve">הופה, מלך הטיטאנים. קלף ענק וחזק. מושלם למשבצת המלך.</t>
         </is>
       </c>
       <c r="E1090" s="3"/>
@@ -25473,7 +25473,7 @@
     <row r="1091">
       <c r="A1091" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s559179f</t>
+          <t xml:space="preserve">s7f80400</t>
         </is>
       </c>
       <c r="C1091" s="2" t="inlineStr">
@@ -25483,7 +25483,7 @@
       </c>
       <c r="D1091" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">אבי-הענקים ביד</t>
+          <t xml:space="preserve">מלך הטיטאנים ביד</t>
         </is>
       </c>
       <c r="E1091" s="3"/>
@@ -26278,7 +26278,7 @@
     <row r="1126">
       <c r="A1126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s8e82b1e</t>
+          <t xml:space="preserve">s9bc09d1</t>
         </is>
       </c>
       <c r="C1126" s="2" t="inlineStr">
@@ -26288,7 +26288,7 @@
       </c>
       <c r="D1126" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">אבי-הענקים. למשבצת המלך, כמו בפעם הקודמת.</t>
+          <t xml:space="preserve">מלך הטיטאנים. למשבצת המלך, כמו בפעם הקודמת.</t>
         </is>
       </c>
       <c r="E1126" s="3"/>
@@ -26301,7 +26301,7 @@
     <row r="1127">
       <c r="A1127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s33be16b</t>
+          <t xml:space="preserve">sccdcf9a</t>
         </is>
       </c>
       <c r="C1127" s="2" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="D1127" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">אבי-הענקים ביד</t>
+          <t xml:space="preserve">מלך הטיטאנים ביד</t>
         </is>
       </c>
       <c r="E1127" s="3"/>

--- a/docs/COPY.xlsx
+++ b/docs/COPY.xlsx
@@ -21241,7 +21241,7 @@
     <row r="907">
       <c r="A907" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s4fc5b19</t>
+          <t xml:space="preserve">s096f0c1</t>
         </is>
       </c>
       <c r="C907" s="2" t="inlineStr">
@@ -21251,13 +21251,13 @@
       </c>
       <c r="D907" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">אמנדה — הצצה</t>
+          <t xml:space="preserve">אמנדה</t>
         </is>
       </c>
       <c r="E907" s="3"/>
       <c r="F907" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">A peek at Amanda</t>
+          <t xml:space="preserve">Amanda</t>
         </is>
       </c>
     </row>

--- a/docs/COPY.xlsx
+++ b/docs/COPY.xlsx
@@ -21241,7 +21241,7 @@
     <row r="907">
       <c r="A907" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s096f0c1</t>
+          <t xml:space="preserve">se4e1ef0</t>
         </is>
       </c>
       <c r="C907" s="2" t="inlineStr">
@@ -21251,20 +21251,20 @@
       </c>
       <c r="D907" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">אמנדה</t>
+          <t xml:space="preserve">דראפט</t>
         </is>
       </c>
       <c r="E907" s="3"/>
       <c r="F907" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Amanda</t>
+          <t xml:space="preserve">Draft</t>
         </is>
       </c>
     </row>
     <row r="908">
       <c r="A908" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s7767343</t>
+          <t xml:space="preserve">s4b7da7f</t>
         </is>
       </c>
       <c r="C908" s="2" t="inlineStr">
@@ -21274,20 +21274,20 @@
       </c>
       <c r="D908" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">מולה לבד. אי אפשר לנצח.</t>
+          <t xml:space="preserve">מה שלא לקחת הולך ליריב.</t>
         </is>
       </c>
       <c r="E908" s="3"/>
       <c r="F908" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">You, on your own, against her. You lose.</t>
+          <t xml:space="preserve">What you leave, they get.</t>
         </is>
       </c>
     </row>
     <row r="909">
       <c r="A909" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s7c9fba9</t>
+          <t xml:space="preserve">se14e946</t>
         </is>
       </c>
       <c r="C909" s="2" t="inlineStr">
@@ -21297,20 +21297,20 @@
       </c>
       <c r="D909" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">דק זהה</t>
+          <t xml:space="preserve">2 נגד 2</t>
         </is>
       </c>
       <c r="E909" s="3"/>
       <c r="F909" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same deck</t>
+          <t xml:space="preserve">2 against 2</t>
         </is>
       </c>
     </row>
     <row r="910">
       <c r="A910" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">secbb695</t>
+          <t xml:space="preserve">sac17390</t>
         </is>
       </c>
       <c r="C910" s="2" t="inlineStr">
@@ -21320,20 +21320,20 @@
       </c>
       <c r="D910" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">אותם קלפים לשני הצדדים.</t>
+          <t xml:space="preserve">שניים בונים לוח אחד.</t>
         </is>
       </c>
       <c r="E910" s="3"/>
       <c r="F910" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Same cards, both sides.</t>
+          <t xml:space="preserve">Two of you, one board.</t>
         </is>
       </c>
     </row>
     <row r="911">
       <c r="A911" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">se14e946</t>
+          <t xml:space="preserve">s7c9fba9</t>
         </is>
       </c>
       <c r="C911" s="2" t="inlineStr">
@@ -21343,20 +21343,20 @@
       </c>
       <c r="D911" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 נגד 2</t>
+          <t xml:space="preserve">דק זהה</t>
         </is>
       </c>
       <c r="E911" s="3"/>
       <c r="F911" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2 against 2</t>
+          <t xml:space="preserve">Same deck</t>
         </is>
       </c>
     </row>
     <row r="912">
       <c r="A912" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">sac17390</t>
+          <t xml:space="preserve">secbb695</t>
         </is>
       </c>
       <c r="C912" s="2" t="inlineStr">
@@ -21366,20 +21366,20 @@
       </c>
       <c r="D912" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">שניים בונים לוח אחד.</t>
+          <t xml:space="preserve">אותם קלפים לשני הצדדים.</t>
         </is>
       </c>
       <c r="E912" s="3"/>
       <c r="F912" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Two of you, one board.</t>
+          <t xml:space="preserve">Same cards, both sides.</t>
         </is>
       </c>
     </row>
     <row r="913">
       <c r="A913" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">se4e1ef0</t>
+          <t xml:space="preserve">s096f0c1</t>
         </is>
       </c>
       <c r="C913" s="2" t="inlineStr">
@@ -21389,20 +21389,20 @@
       </c>
       <c r="D913" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">דראפט</t>
+          <t xml:space="preserve">אמנדה</t>
         </is>
       </c>
       <c r="E913" s="3"/>
       <c r="F913" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">Draft</t>
+          <t xml:space="preserve">Amanda</t>
         </is>
       </c>
     </row>
     <row r="914">
       <c r="A914" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s4b7da7f</t>
+          <t xml:space="preserve">s7767343</t>
         </is>
       </c>
       <c r="C914" s="2" t="inlineStr">
@@ -21412,13 +21412,13 @@
       </c>
       <c r="D914" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">מה שלא לקחת הולך ליריב.</t>
+          <t xml:space="preserve">מולה לבד. אי אפשר לנצח.</t>
         </is>
       </c>
       <c r="E914" s="3"/>
       <c r="F914" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">What you leave, they get.</t>
+          <t xml:space="preserve">You, on your own, against her. You lose.</t>
         </is>
       </c>
     </row>
@@ -21977,7 +21977,7 @@
     <row r="939">
       <c r="A939" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s937aed8</t>
+          <t xml:space="preserve">s6ddcdaa</t>
         </is>
       </c>
       <c r="C939" s="2" t="inlineStr">
@@ -21987,13 +21987,13 @@
       </c>
       <c r="D939" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">עוד {0} נאצ'וס ותיבה</t>
+          <t xml:space="preserve">עוד {0} נאצ'וס לתיבה</t>
         </is>
       </c>
       <c r="E939" s="3"/>
       <c r="F939" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">{0} more nachos and a chest is yours</t>
+          <t xml:space="preserve">{0} more nachos to a chest</t>
         </is>
       </c>
     </row>

--- a/docs/COPY.xlsx
+++ b/docs/COPY.xlsx
@@ -16319,7 +16319,7 @@
     <row r="693">
       <c r="A693" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">s4f9261a</t>
+          <t xml:space="preserve">sac15acb</t>
         </is>
       </c>
       <c r="C693" s="2" t="inlineStr">
@@ -16329,7 +16329,7 @@
       </c>
       <c r="D693" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">לשדרוג</t>
+          <t xml:space="preserve">שדרוג</t>
         </is>
       </c>
       <c r="E693" s="3"/>
